--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>ATGL</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -712,14 +712,14 @@
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>300</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -741,14 +741,14 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>200</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -770,14 +770,14 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -870,26 +870,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -899,26 +899,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -938,14 +938,14 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>400</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -967,14 +967,14 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-100</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1009,14 +1009,14 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1038,8 +1038,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-300</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>3</v>
@@ -1067,14 +1067,14 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1096,14 +1096,14 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-100</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1125,14 +1125,14 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1183,14 +1183,14 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-100</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1212,14 +1212,14 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-100</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1270,26 +1270,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1357,14 +1357,14 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1386,14 +1386,14 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-100</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1444,14 +1444,14 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-100</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1533,8 +1533,8 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>1500</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>3</v>
@@ -1562,26 +1562,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1591,8 +1591,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -1620,26 +1620,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1649,8 +1649,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -1678,8 +1678,8 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>3</v>
+      <c r="D46" s="3">
+        <v>1700</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>3</v>
@@ -1707,26 +1707,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1736,8 +1736,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -1765,8 +1765,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>2000</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>3</v>
@@ -1852,8 +1852,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>2000</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -1910,8 +1910,8 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>3</v>
+      <c r="D54" s="3">
+        <v>5600</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -1965,26 +1965,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -1994,8 +1994,8 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>100</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
@@ -2023,8 +2023,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>2300</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -2052,8 +2052,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>2400</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>3</v>
@@ -2082,7 +2082,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2110,26 +2110,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2226,8 +2226,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>2600</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>3</v>
@@ -2326,26 +2326,26 @@
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>3</v>
+      <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>3</v>
@@ -2384,8 +2384,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>1800</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>3</v>
@@ -2500,8 +2500,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>3100</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>3</v>
@@ -2592,14 +2592,14 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-100</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2634,8 +2634,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
@@ -2808,8 +2808,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>100</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>3</v>
@@ -2937,8 +2937,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-1300</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
@@ -3095,8 +3095,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>2300</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -3124,26 +3124,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3153,8 +3153,8 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>1100</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>ATGL</t>
   </si>
@@ -656,45 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -707,23 +708,26 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -736,23 +740,26 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,22 +772,25 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -794,8 +804,11 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,8 +820,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -836,8 +850,11 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,8 +882,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,40 +911,46 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,23 +959,24 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,23 +989,26 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
       </c>
       <c r="F18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -991,8 +1021,11 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1037,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1018,8 +1052,8 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1033,17 +1067,20 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1099,11 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1076,8 +1116,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1091,23 +1131,26 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E23" s="3">
         <v>-300</v>
       </c>
       <c r="F23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,8 +1163,11 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1134,8 +1180,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1149,8 +1195,11 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,23 +1227,26 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
         <v>-300</v>
       </c>
       <c r="F26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1207,23 +1259,26 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
         <v>-300</v>
       </c>
       <c r="F27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1236,8 +1291,11 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1323,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,11 +1352,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1387,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,8 +1419,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1366,8 +1436,8 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1381,23 +1451,26 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E33" s="3">
         <v>-300</v>
       </c>
       <c r="F33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1410,8 +1483,11 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,23 +1515,26 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E35" s="3">
         <v>-300</v>
       </c>
       <c r="F35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,28 +1547,31 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1502,8 +1584,11 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1600,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,17 +1614,18 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1557,8 +1644,11 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1583,19 +1673,22 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1615,8 +1708,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1641,20 +1737,23 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,17 +1772,20 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1700</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1702,8 +1804,11 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1728,19 +1833,22 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
         <v>0</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+      <c r="E48" s="3">
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1760,17 +1868,20 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2000</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1789,8 +1900,11 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +1932,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,17 +1964,20 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,8 +1996,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,17 +2028,20 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5600</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1934,8 +2060,11 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2076,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,8 +2090,9 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -1986,19 +2117,22 @@
       <c r="J57" s="3">
         <v>0</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="E58" s="3">
+        <v>100</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2018,17 +2152,20 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2047,17 +2184,20 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,17 +2216,20 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -2105,8 +2248,11 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2131,11 +2277,14 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2312,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2344,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,17 +2376,20 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2600</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2250,8 +2408,11 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2424,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2454,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,8 +2486,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,11 +2515,14 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,17 +2550,20 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1800</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2408,8 +2582,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +2614,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +2646,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,17 +2678,20 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3100</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,8 +2710,11 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,28 +2742,31 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2587,23 +2779,26 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="E81" s="3">
         <v>-300</v>
       </c>
       <c r="F81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2616,8 +2811,11 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,16 +2827,17 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2658,8 +2857,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +2889,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +2921,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +2953,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +2985,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,17 +3017,20 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
@@ -2832,8 +3049,11 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,8 +3065,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2874,8 +3095,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3127,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,16 +3159,19 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>-1300</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -2961,8 +3191,11 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,8 +3207,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3003,8 +3237,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3269,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +3301,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,17 +3333,20 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>2300</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3119,8 +3365,11 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3145,20 +3394,23 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,6 +3427,9 @@
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -2040,7 +2040,7 @@
         <v>5200</v>
       </c>
       <c r="E54" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>ATGL</t>
   </si>
@@ -656,86 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F8" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
-        <v>300</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -743,31 +750,37 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -775,13 +788,19 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
@@ -792,14 +811,14 @@
       <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -807,8 +826,14 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,8 +846,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -853,8 +880,14 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,8 +918,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -903,54 +942,66 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,31 +1011,33 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="E17" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="F17" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="G17" s="3">
+        <v>500</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+      <c r="I17" s="3">
+        <v>400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>200</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -992,40 +1045,52 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
       </c>
       <c r="F18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,16 +1103,18 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1055,14 +1122,14 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1070,31 +1137,37 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="F21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1102,8 +1175,14 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1119,14 +1198,14 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1134,13 +1213,19 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E23" s="3">
         <v>-300</v>
@@ -1149,16 +1234,16 @@
         <v>-300</v>
       </c>
       <c r="G23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="I23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-100</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1166,16 +1251,22 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1183,14 +1274,14 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1198,8 +1289,14 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,13 +1327,19 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E26" s="3">
         <v>-300</v>
@@ -1245,30 +1348,36 @@
         <v>-300</v>
       </c>
       <c r="G26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E27" s="3">
         <v>-300</v>
@@ -1277,25 +1386,31 @@
         <v>-300</v>
       </c>
       <c r="G27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1441,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1355,11 +1476,17 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1517,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,16 +1555,22 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1439,14 +1578,14 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1454,13 +1593,19 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E33" s="3">
         <v>-300</v>
@@ -1469,25 +1614,31 @@
         <v>-300</v>
       </c>
       <c r="G33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,13 +1669,19 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E35" s="3">
         <v>-300</v>
@@ -1533,62 +1690,74 @@
         <v>-300</v>
       </c>
       <c r="G35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1770,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,31 +1786,33 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>500</v>
+      </c>
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>400</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1647,8 +1820,14 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1676,11 +1855,17 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1688,22 +1873,22 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>200</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1711,63 +1896,75 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2700</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="F45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1775,31 +1972,37 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F46" s="3">
         <v>3300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H46" s="3">
         <v>1700</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>800</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1807,40 +2010,52 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1850,20 +2065,20 @@
       <c r="E48" s="3">
         <v>0</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1871,8 +2086,14 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1880,22 +2101,22 @@
         <v>1900</v>
       </c>
       <c r="E49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I49" s="3">
         <v>2000</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1903,8 +2124,14 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2162,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,16 +2200,22 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>2000</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1999,8 +2238,14 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,31 +2276,37 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F54" s="3">
         <v>5200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I54" s="3">
         <v>5700</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="J54" s="3">
+        <v>800</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2063,8 +2314,14 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2334,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,40 +2350,48 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2134,20 +2401,20 @@
       <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2155,31 +2422,37 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2500</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>2300</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>800</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2187,31 +2460,37 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1200</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2219,8 +2498,14 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2228,22 +2513,22 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>100</v>
+      </c>
+      <c r="G61" s="3">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2251,40 +2536,52 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2612,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2650,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,31 +2688,37 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2411,8 +2726,14 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2746,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2780,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2818,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2518,11 +2853,17 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,31 +2894,37 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1200</v>
+        <v>-1500</v>
       </c>
       <c r="E72" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-500</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2585,8 +2932,14 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2970,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +3008,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,31 +3046,37 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F76" s="3">
         <v>2500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H76" s="3">
         <v>3100</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-500</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2713,8 +3084,14 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,50 +3122,62 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="E81" s="3">
         <v>-300</v>
@@ -2797,25 +3186,31 @@
         <v>-300</v>
       </c>
       <c r="G81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,28 +3223,30 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -2860,8 +3257,14 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3295,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3333,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3371,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3409,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,31 +3447,37 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>500</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
+        <v>200</v>
+      </c>
+      <c r="G89" s="3">
+        <v>200</v>
+      </c>
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3052,8 +3485,14 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,16 +3505,18 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -3083,11 +3524,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -3098,8 +3539,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3577,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,31 +3615,37 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3194,8 +3653,14 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,31 +3673,33 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3240,8 +3707,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3745,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3783,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,31 +3821,37 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>900</v>
-      </c>
-      <c r="E100" s="3">
-        <v>2300</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3368,68 +3859,86 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>500</v>
+      </c>
+      <c r="I102" s="3">
+        <v>600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>ATGL</t>
   </si>
@@ -656,70 +656,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -730,34 +738,40 @@
         <v>400</v>
       </c>
       <c r="F8" s="3">
+        <v>400</v>
+      </c>
+      <c r="G8" s="3">
+        <v>400</v>
+      </c>
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,34 +782,40 @@
         <v>200</v>
       </c>
       <c r="F9" s="3">
+        <v>200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,10 +826,10 @@
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -818,13 +838,13 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -832,8 +852,14 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,8 +874,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -886,8 +914,14 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -924,16 +958,22 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -947,23 +987,29 @@
       <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>200</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -988,20 +1034,26 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1013,54 +1065,62 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>500</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
         <v>-300</v>
@@ -1069,28 +1129,34 @@
         <v>-300</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1105,37 +1171,39 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1143,16 +1211,22 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
         <v>-300</v>
@@ -1161,28 +1235,34 @@
         <v>-300</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1207,11 +1287,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1219,16 +1299,22 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>-300</v>
@@ -1237,19 +1323,19 @@
         <v>-300</v>
       </c>
       <c r="H23" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="I23" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-100</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1257,8 +1343,14 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1268,11 +1360,11 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1283,11 +1375,11 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1295,8 +1387,14 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1333,16 +1431,22 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
         <v>-300</v>
@@ -1351,36 +1455,42 @@
         <v>-300</v>
       </c>
       <c r="H26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
         <v>-300</v>
@@ -1389,28 +1499,34 @@
         <v>-300</v>
       </c>
       <c r="H27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1447,8 +1563,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1482,11 +1604,17 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1523,8 +1651,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1561,37 +1695,43 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1599,16 +1739,22 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
         <v>-300</v>
@@ -1617,28 +1763,34 @@
         <v>-300</v>
       </c>
       <c r="H33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1675,16 +1827,22 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
         <v>-300</v>
@@ -1693,71 +1851,83 @@
         <v>-300</v>
       </c>
       <c r="H35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1772,8 +1942,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1788,46 +1960,54 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F41" s="3">
         <v>5600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1861,19 +2041,25 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -1882,28 +2068,34 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1928,49 +2120,55 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
+        <v>200</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
@@ -1978,46 +2176,58 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F46" s="3">
         <v>5800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2042,28 +2252,34 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
@@ -2078,30 +2294,36 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="F49" s="3">
         <v>1900</v>
@@ -2113,16 +2335,16 @@
         <v>1900</v>
       </c>
       <c r="I49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K49" s="3">
         <v>2000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2130,8 +2352,14 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2168,8 +2396,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2206,16 +2440,22 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2484,14 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2282,8 +2528,14 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2294,34 +2546,40 @@
         <v>7700</v>
       </c>
       <c r="F54" s="3">
+        <v>7700</v>
+      </c>
+      <c r="G54" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H54" s="3">
         <v>5200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2336,8 +2594,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2352,8 +2612,10 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2378,28 +2640,34 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
@@ -2414,106 +2682,124 @@
         <v>100</v>
       </c>
       <c r="J58" s="3">
+        <v>100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>100</v>
+      </c>
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -2522,19 +2808,19 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>200</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -2542,8 +2828,14 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2568,20 +2860,26 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2618,8 +2916,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2656,8 +2960,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2694,8 +3004,14 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2703,37 +3019,43 @@
         <v>1100</v>
       </c>
       <c r="E66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F66" s="3">
         <v>1100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2748,8 +3070,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2786,8 +3110,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2824,8 +3154,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2859,11 +3195,17 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2900,46 +3242,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2976,8 +3330,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3014,8 +3374,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3052,46 +3418,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F76" s="3">
         <v>6700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3128,59 +3506,71 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F81" s="3">
         <v>-300</v>
@@ -3189,28 +3579,34 @@
         <v>-300</v>
       </c>
       <c r="H81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3225,16 +3621,18 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3248,11 +3646,11 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3263,8 +3661,14 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3301,8 +3705,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3339,8 +3749,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3377,8 +3793,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3415,8 +3837,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3453,8 +3881,14 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3464,26 +3898,26 @@
       <c r="E89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3">
-        <v>200</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -3491,8 +3925,14 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3507,8 +3947,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3518,23 +3960,23 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3545,8 +3987,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3583,8 +4031,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3621,8 +4075,14 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3632,26 +4092,26 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -3659,8 +4119,14 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3675,8 +4141,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3701,11 +4169,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3713,8 +4181,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3751,8 +4225,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3789,8 +4269,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3827,8 +4313,14 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3838,26 +4330,26 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -3865,8 +4357,14 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3891,20 +4389,26 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3915,30 +4419,36 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>ATGL</t>
   </si>
@@ -737,11 +737,11 @@
       <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
-        <v>400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>400</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
@@ -781,11 +781,11 @@
       <c r="E9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
-        <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>200</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -825,11 +825,11 @@
       <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -975,11 +975,11 @@
       <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>200</v>
@@ -1078,11 +1078,11 @@
       <c r="E17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="3">
-        <v>700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>700</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>500</v>
@@ -1122,11 +1122,11 @@
       <c r="E18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
@@ -1184,11 +1184,11 @@
       <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-200</v>
@@ -1229,10 +1229,10 @@
         <v>100</v>
       </c>
       <c r="F21" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-100</v>
@@ -1272,11 +1272,11 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       <c r="E23" s="3">
         <v>0</v>
       </c>
-      <c r="F23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-300</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-300</v>
@@ -1448,11 +1448,11 @@
       <c r="E26" s="3">
         <v>0</v>
       </c>
-      <c r="F26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-300</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-300</v>
@@ -1492,11 +1492,11 @@
       <c r="E27" s="3">
         <v>0</v>
       </c>
-      <c r="F27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-300</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-300</v>
@@ -1712,11 +1712,11 @@
       <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>200</v>
@@ -1756,11 +1756,11 @@
       <c r="E33" s="3">
         <v>0</v>
       </c>
-      <c r="F33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-300</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-300</v>
@@ -1844,11 +1844,11 @@
       <c r="E35" s="3">
         <v>0</v>
       </c>
-      <c r="F35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-300</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-300</v>
@@ -1973,11 +1973,11 @@
       <c r="E41" s="3">
         <v>5400</v>
       </c>
-      <c r="F41" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>5600</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>500</v>
@@ -2061,11 +2061,11 @@
       <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
-        <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>100</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -2149,11 +2149,11 @@
       <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>2700</v>
@@ -2193,11 +2193,11 @@
       <c r="E46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>5800</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>3300</v>
@@ -2281,11 +2281,11 @@
       <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -2325,11 +2325,11 @@
       <c r="E49" s="3">
         <v>1800</v>
       </c>
-      <c r="F49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1900</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>1900</v>
@@ -2545,11 +2545,11 @@
       <c r="E54" s="3">
         <v>7700</v>
       </c>
-      <c r="F54" s="3">
-        <v>7700</v>
-      </c>
-      <c r="G54" s="3">
-        <v>7700</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>5200</v>
@@ -2669,11 +2669,11 @@
       <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
-        <v>100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>100</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
@@ -2713,11 +2713,11 @@
       <c r="E59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
-        <v>700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>700</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>1000</v>
@@ -2757,11 +2757,11 @@
       <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1000</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>2600</v>
@@ -2802,10 +2802,10 @@
         <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
@@ -3021,11 +3021,11 @@
       <c r="E66" s="3">
         <v>1000</v>
       </c>
-      <c r="F66" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1100</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>2700</v>
@@ -3259,11 +3259,11 @@
       <c r="E72" s="3">
         <v>-1600</v>
       </c>
-      <c r="F72" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1500</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-900</v>
@@ -3435,11 +3435,11 @@
       <c r="E76" s="3">
         <v>6600</v>
       </c>
-      <c r="F76" s="3">
-        <v>6700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>6700</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>2500</v>
@@ -3572,11 +3572,11 @@
       <c r="E81" s="3">
         <v>0</v>
       </c>
-      <c r="F81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-300</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-300</v>
@@ -3640,14 +3640,14 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>ATGL</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -666,46 +666,48 @@
     <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44834</v>
       </c>
       <c r="K7" s="2">
         <v>44926</v>
@@ -713,11 +715,11 @@
       <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
+      <c r="M7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N7" s="2">
+        <v>44834</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
@@ -725,31 +727,37 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>400</v>
@@ -757,11 +765,11 @@
       <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
+      <c r="M8" s="3">
+        <v>400</v>
+      </c>
+      <c r="N8" s="3">
+        <v>100</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
@@ -769,31 +777,37 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
@@ -801,11 +815,11 @@
       <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
+      <c r="M9" s="3">
+        <v>200</v>
+      </c>
+      <c r="N9" s="3">
+        <v>100</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
@@ -813,22 +827,28 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -837,7 +857,7 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -845,11 +865,11 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
@@ -857,8 +877,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +901,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +947,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,22 +997,28 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>900</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>200</v>
       </c>
       <c r="H14" s="3">
         <v>200</v>
@@ -986,8 +1026,8 @@
       <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>200</v>
       </c>
       <c r="K14" s="3">
         <v>200</v>
@@ -996,19 +1036,25 @@
         <v>3</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1039,20 +1085,26 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,16 +1118,18 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>500</v>
+        <v>3600</v>
       </c>
       <c r="E17" s="3">
-        <v>500</v>
+        <v>3600</v>
       </c>
       <c r="F17" s="3">
         <v>500</v>
@@ -1084,13 +1138,13 @@
         <v>500</v>
       </c>
       <c r="H17" s="3">
+        <v>500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>500</v>
+      </c>
+      <c r="J17" s="3">
         <v>400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>200</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
@@ -1098,11 +1152,11 @@
       <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>400</v>
+      </c>
+      <c r="N17" s="3">
+        <v>200</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
@@ -1110,31 +1164,37 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -1142,11 +1202,11 @@
       <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-100</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1154,8 +1214,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,29 +1238,31 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1204,11 +1272,11 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1216,31 +1284,37 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1248,11 +1322,11 @@
       <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-100</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
@@ -1260,8 +1334,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1292,11 +1372,11 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1304,28 +1384,34 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-100</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
@@ -1336,11 +1422,11 @@
       <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-100</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1348,22 +1434,28 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1380,11 +1472,11 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1392,8 +1484,14 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,31 +1534,37 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-100</v>
       </c>
       <c r="K26" s="3">
         <v>-200</v>
@@ -1468,11 +1572,11 @@
       <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-100</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
@@ -1480,31 +1584,37 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-100</v>
       </c>
       <c r="K27" s="3">
         <v>-200</v>
@@ -1512,11 +1622,11 @@
       <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-100</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
@@ -1524,8 +1634,14 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1684,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1609,11 +1731,17 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1784,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,29 +1834,35 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -1732,11 +1872,11 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1744,31 +1884,37 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-100</v>
       </c>
       <c r="K33" s="3">
         <v>-200</v>
@@ -1776,11 +1922,11 @@
       <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-100</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
@@ -1788,8 +1934,14 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,31 +1984,37 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-100</v>
       </c>
       <c r="K35" s="3">
         <v>-200</v>
@@ -1864,11 +2022,11 @@
       <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-100</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
@@ -1876,36 +2034,42 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44834</v>
       </c>
       <c r="K38" s="2">
         <v>44926</v>
@@ -1913,11 +2077,11 @@
       <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
+      <c r="M38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N38" s="2">
+        <v>44834</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
@@ -1925,8 +2089,14 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2113,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,31 +2133,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>400</v>
       </c>
       <c r="K41" s="3">
         <v>1500</v>
@@ -1993,11 +2167,11 @@
       <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N41" s="3">
+        <v>400</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
@@ -2005,8 +2179,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2046,34 +2226,40 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2081,11 +2267,11 @@
       <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>200</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2093,8 +2279,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2125,20 +2317,26 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2149,16 +2347,16 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
@@ -2169,11 +2367,11 @@
       <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
+        <v>200</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2181,31 +2379,37 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F46" s="3">
         <v>5600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J46" s="3">
-        <v>800</v>
       </c>
       <c r="K46" s="3">
         <v>1700</v>
@@ -2213,11 +2417,11 @@
       <c r="L46" s="3">
         <v>800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="M46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N46" s="3">
+        <v>800</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
@@ -2225,8 +2429,14 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2257,20 +2467,26 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2281,10 +2497,10 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -2293,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2301,11 +2517,11 @@
       <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>100</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2313,31 +2529,37 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>1800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1900</v>
       </c>
       <c r="H49" s="3">
         <v>1900</v>
       </c>
       <c r="I49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K49" s="3">
         <v>2000</v>
@@ -2345,11 +2567,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2357,8 +2579,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2629,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,8 +2679,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2456,11 +2696,11 @@
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2489,8 +2729,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,31 +2779,37 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F54" s="3">
         <v>7700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J54" s="3">
-        <v>800</v>
       </c>
       <c r="K54" s="3">
         <v>5700</v>
@@ -2565,11 +2817,11 @@
       <c r="L54" s="3">
         <v>800</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
+      <c r="M54" s="3">
+        <v>5700</v>
+      </c>
+      <c r="N54" s="3">
+        <v>800</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
@@ -2577,8 +2829,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2853,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,16 +2873,18 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2645,34 +2907,40 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
@@ -2687,22 +2955,28 @@
         <v>100</v>
       </c>
       <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="3">
+        <v>100</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2713,19 +2987,19 @@
         <v>500</v>
       </c>
       <c r="F59" s="3">
+        <v>500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>800</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
@@ -2733,11 +3007,11 @@
       <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>700</v>
+      </c>
+      <c r="N59" s="3">
+        <v>800</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -2745,31 +3019,37 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1200</v>
       </c>
       <c r="K60" s="3">
         <v>2400</v>
@@ -2777,11 +3057,11 @@
       <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
+      <c r="M60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N60" s="3">
+        <v>1200</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
@@ -2789,28 +3069,34 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>200</v>
       </c>
       <c r="J61" s="3">
         <v>200</v>
@@ -2822,10 +3108,10 @@
         <v>200</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -2833,8 +3119,14 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2865,20 +3157,26 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3219,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3269,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,31 +3319,37 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1400</v>
       </c>
       <c r="K66" s="3">
         <v>2600</v>
@@ -3041,11 +3357,11 @@
       <c r="L66" s="3">
         <v>1400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="M66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N66" s="3">
+        <v>1400</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
@@ -3053,8 +3369,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3393,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3439,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3489,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3200,11 +3536,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,31 +3589,37 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-500</v>
       </c>
       <c r="K72" s="3">
         <v>-300</v>
@@ -3279,11 +3627,11 @@
       <c r="L72" s="3">
         <v>-500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-500</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3291,8 +3639,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3689,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3739,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,31 +3789,37 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F76" s="3">
         <v>6600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-500</v>
       </c>
       <c r="K76" s="3">
         <v>3100</v>
@@ -3455,11 +3827,11 @@
       <c r="L76" s="3">
         <v>-500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-500</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3839,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,36 +3889,42 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44834</v>
       </c>
       <c r="K80" s="2">
         <v>44926</v>
@@ -3548,11 +3932,11 @@
       <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
+      <c r="M80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N80" s="2">
+        <v>44834</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
@@ -3560,31 +3944,37 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-100</v>
       </c>
       <c r="K81" s="3">
         <v>-200</v>
@@ -3592,11 +3982,11 @@
       <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-100</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
@@ -3604,8 +3994,14 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,22 +4018,24 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3648,14 +4046,14 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3666,8 +4064,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +4114,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +4164,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4214,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4264,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,43 +4314,49 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-500</v>
       </c>
       <c r="F89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>100</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
+        <v>100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -3930,8 +4364,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,25 +4388,27 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3977,11 +4419,11 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3992,8 +4434,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4484,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,43 +4534,49 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4124,8 +4584,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,8 +4608,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4174,11 +4642,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4186,8 +4654,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4704,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4754,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,43 +4804,49 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>100</v>
       </c>
       <c r="F100" s="3">
+        <v>100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>100</v>
+      </c>
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>1100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>1100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4362,8 +4854,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4394,43 +4892,49 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="F102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>500</v>
-      </c>
-      <c r="I102" s="3">
-        <v>600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>600</v>
@@ -4438,16 +4942,22 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>600</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
